--- a/test/matrice_tests.xlsx
+++ b/test/matrice_tests.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>v2.0.0</t>
+          <t>v2.1.0</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-19 07:32</t>
+          <t>2026-05-27 00:32</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>62 tests doivent rester verts</t>
+          <t>120 tests doivent rester verts (90 v2.0 + 30 licensing v2.1)</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>62 passed, 0 failed</t>
+          <t>120 passed, 0 failed</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr"/>
